--- a/output/nav_changes_2026-03-16.xlsx
+++ b/output/nav_changes_2026-03-16.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TMX:DYN27550</t>
+          <t>0P0001ROZ4.TO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -560,22 +560,16 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>15.95</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>8.8093</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>8.819000000000001</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>-0.0011</v>
       </c>
     </row>
     <row r="4">
@@ -1079,8 +1073,8 @@
       <c r="N2" s="6" t="n">
         <v>-0.0003790000000000001</v>
       </c>
-      <c r="O2" s="7" t="n">
-        <v>0</v>
+      <c r="O2" s="6" t="n">
+        <v>-0.0011</v>
       </c>
     </row>
     <row r="3">
@@ -1128,7 +1122,9 @@
       <c r="N3" s="6" t="n">
         <v>-0.00292</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" s="6" t="n">
+        <v>-0.001721</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1175,7 +1171,9 @@
       <c r="N4" s="6" t="n">
         <v>-0.003277</v>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" s="6" t="n">
+        <v>-0.000407</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1222,7 +1220,9 @@
       <c r="N5" s="10" t="n">
         <v>0.000285</v>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" s="10" t="n">
+        <v>0.000374</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1269,7 +1269,9 @@
       <c r="N6" s="10" t="n">
         <v>0.0009779999999999999</v>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" s="10" t="n">
+        <v>0.000215</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1316,7 +1318,9 @@
       <c r="N7" s="6" t="n">
         <v>-0.002977</v>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" s="6" t="n">
+        <v>-0.001165</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1363,7 +1367,9 @@
       <c r="N8" s="6" t="n">
         <v>-0.002675</v>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" s="6" t="n">
+        <v>-0.001051</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1410,7 +1416,9 @@
       <c r="N9" s="10" t="n">
         <v>0.0005369999999999999</v>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" s="10" t="n">
+        <v>8.999999999999999e-05</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1457,7 +1465,9 @@
       <c r="N10" s="6" t="n">
         <v>-0.002377</v>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" s="6" t="n">
+        <v>-0.001354</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1504,7 +1514,9 @@
       <c r="N11" s="6" t="n">
         <v>-0.003236</v>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" s="6" t="n">
+        <v>-0.002049</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1551,7 +1563,9 @@
       <c r="N12" s="10" t="n">
         <v>5e-05</v>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" s="10" t="n">
+        <v>0.0008899999999999999</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1598,7 +1612,9 @@
       <c r="N13" s="10" t="n">
         <v>0.0007570000000000001</v>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" s="10" t="n">
+        <v>0.00062</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1645,7 +1661,9 @@
       <c r="N14" s="6" t="n">
         <v>-0.000202</v>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" s="10" t="n">
+        <v>0.000214</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1692,7 +1710,9 @@
       <c r="N15" s="10" t="n">
         <v>4e-05</v>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" s="6" t="n">
+        <v>-0.000169</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1739,7 +1759,9 @@
       <c r="N16" s="10" t="n">
         <v>0.00098</v>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" s="10" t="n">
+        <v>0.0008010000000000001</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1786,7 +1808,9 @@
       <c r="N17" s="10" t="n">
         <v>0.000445</v>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" s="6" t="n">
+        <v>-4.5e-05</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1833,7 +1857,9 @@
       <c r="N18" s="10" t="n">
         <v>1e-05</v>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" s="10" t="n">
+        <v>0.000181</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1880,7 +1906,9 @@
       <c r="N19" s="10" t="n">
         <v>0.000283</v>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" s="6" t="n">
+        <v>-3.4e-05</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1927,7 +1955,9 @@
       <c r="N20" s="10" t="n">
         <v>0.000779</v>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" s="10" t="n">
+        <v>0.00044</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1974,7 +2004,9 @@
       <c r="N21" s="10" t="n">
         <v>0.001012</v>
       </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" s="10" t="n">
+        <v>0.000384</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2021,7 +2053,9 @@
       <c r="N22" s="10" t="n">
         <v>0.002059</v>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" s="10" t="n">
+        <v>0.000723</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2068,7 +2102,9 @@
       <c r="N23" s="10" t="n">
         <v>0.000365</v>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" s="6" t="n">
+        <v>-0.000825</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2115,7 +2151,9 @@
       <c r="N24" s="10" t="n">
         <v>0.001219</v>
       </c>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" s="10" t="n">
+        <v>0.000746</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2162,7 +2200,9 @@
       <c r="N25" s="6" t="n">
         <v>-0.000163</v>
       </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" s="10" t="n">
+        <v>0.000317</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2209,7 +2249,9 @@
       <c r="N26" s="10" t="n">
         <v>0.000163</v>
       </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" s="10" t="n">
+        <v>0.000396</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2256,7 +2298,9 @@
       <c r="N27" s="10" t="n">
         <v>0.001058</v>
       </c>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" s="10" t="n">
+        <v>0.000339</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2303,7 +2347,9 @@
       <c r="N28" s="10" t="n">
         <v>0.000122</v>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" s="10" t="n">
+        <v>0.000623</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2350,7 +2396,9 @@
       <c r="N29" s="6" t="n">
         <v>-0.000122</v>
       </c>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" s="10" t="n">
+        <v>0.00026</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2397,7 +2445,9 @@
       <c r="N30" s="10" t="n">
         <v>0.000376</v>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" s="10" t="n">
+        <v>0.000193</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2444,7 +2494,9 @@
       <c r="N31" s="10" t="n">
         <v>0.000428</v>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" s="10" t="n">
+        <v>0.000136</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2491,7 +2543,9 @@
       <c r="N32" s="6" t="n">
         <v>-0.000204</v>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" s="10" t="n">
+        <v>6.8e-05</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2538,7 +2592,9 @@
       <c r="N33" s="6" t="n">
         <v>-0.000285</v>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" s="10" t="n">
+        <v>0.000159</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2585,7 +2641,9 @@
       <c r="N34" s="6" t="n">
         <v>-0.00126</v>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" s="10" t="n">
+        <v>0.000317</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2632,7 +2690,9 @@
       <c r="N35" s="10" t="n">
         <v>0.001822</v>
       </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" s="10" t="n">
+        <v>0.001158</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2679,7 +2739,9 @@
       <c r="N36" s="6" t="n">
         <v>-0.000326</v>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" s="6" t="n">
+        <v>-0.000272</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2726,7 +2788,9 @@
       <c r="N37" s="10" t="n">
         <v>0.000896</v>
       </c>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" s="10" t="n">
+        <v>0.000931</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2773,7 +2837,9 @@
       <c r="N38" s="10" t="n">
         <v>0.001336</v>
       </c>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" s="10" t="n">
+        <v>0.0007729999999999999</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2818,7 +2884,9 @@
       <c r="N39" s="6" t="n">
         <v>-0.002249</v>
       </c>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" s="6" t="n">
+        <v>-0.0007040000000000001</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2863,7 +2931,9 @@
       <c r="N40" s="6" t="n">
         <v>-0.000478</v>
       </c>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" s="10" t="n">
+        <v>0.000329</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">

--- a/output/nav_changes_2026-03-16.xlsx
+++ b/output/nav_changes_2026-03-16.xlsx
@@ -964,67 +964,67 @@
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
+          <t>Dynamic Credit Abs Return F</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
           <t>Dynamic Short Term Credit PLUS F</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>DXDB Dynamic Discount Bond ETF</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Lysander-Canso Corp Value Bond F</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Lysander-Fulcra Corp Sec F</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Pender Corporate Bond F</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>XIG US IG Corp Bond (CAD Hdg)</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>XCB Cdn Corporate Bond</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>PIMCO Monthly Income F</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Manulife Strategic Income F</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>RBC Global Bond F</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>Mackenzie Unconstrained FI F</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>RBC Core Bond F</t>
-        </is>
-      </c>
-      <c r="O1" s="9" t="inlineStr">
-        <is>
-          <t>Dynamic Credit Abs Return F</t>
         </is>
       </c>
     </row>
@@ -1038,43 +1038,43 @@
         <v>0</v>
       </c>
       <c r="C2" s="6" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="D2" s="6" t="n">
         <v>-0.001998</v>
       </c>
-      <c r="D2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="6" t="n">
         <v>-2.1e-05</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="6" t="n">
         <v>-0.0007159999999999999</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="6" t="n">
         <v>-0.003859</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="6" t="n">
         <v>-0.003593</v>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="J2" s="6" t="n">
         <v>-0.0005</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="6" t="n">
         <v>-0.002208</v>
       </c>
-      <c r="K2" s="6" t="n">
+      <c r="L2" s="6" t="n">
         <v>-0.0007779999999999999</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="6" t="n">
         <v>-0.002196</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="N2" s="6" t="n">
         <v>-0.001369</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="6" t="n">
         <v>-0.0003790000000000001</v>
-      </c>
-      <c r="O2" s="6" t="n">
-        <v>-0.0011</v>
       </c>
     </row>
     <row r="3">
@@ -1087,43 +1087,43 @@
         <v>0</v>
       </c>
       <c r="C3" s="6" t="n">
+        <v>-0.001721</v>
+      </c>
+      <c r="D3" s="6" t="n">
         <v>-0.002491</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="E3" s="6" t="n">
         <v>-0.002328</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="6" t="n">
         <v>-0.003599</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="6" t="n">
         <v>-0.00164</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="6" t="n">
         <v>-0.004332</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="6" t="n">
         <v>-0.006629</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="J3" s="6" t="n">
         <v>-0.00398</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="6" t="n">
         <v>-0.006307</v>
       </c>
-      <c r="K3" s="6" t="n">
+      <c r="L3" s="6" t="n">
         <v>-0.003859</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="6" t="n">
         <v>-0.003517</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="N3" s="6" t="n">
         <v>-0.001958</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="6" t="n">
         <v>-0.00292</v>
-      </c>
-      <c r="O3" s="6" t="n">
-        <v>-0.001721</v>
       </c>
     </row>
     <row r="4">
@@ -1136,43 +1136,43 @@
         <v>0</v>
       </c>
       <c r="C4" s="6" t="n">
+        <v>-0.000407</v>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>-0.001989</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>-0.004634</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="6" t="n">
         <v>-0.00372</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="6" t="n">
         <v>-0.001144</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="6" t="n">
         <v>-0.001293</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="6" t="n">
         <v>-0.007591</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="J4" s="6" t="n">
         <v>-0.005443</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="6" t="n">
         <v>-0.001916</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="L4" s="6" t="n">
         <v>-0.002285</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="6" t="n">
         <v>-0.004531</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="6" t="n">
         <v>-0.002736</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="6" t="n">
         <v>-0.003277</v>
-      </c>
-      <c r="O4" s="6" t="n">
-        <v>-0.000407</v>
       </c>
     </row>
     <row r="5">
@@ -1184,44 +1184,44 @@
       <c r="B5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="10" t="n">
+        <v>0.000374</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>-0.00149</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="E5" s="6" t="n">
         <v>-0.00185</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>-0.000382</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="G5" s="10" t="n">
         <v>0.000378</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="H5" s="10" t="n">
         <v>0.000804</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>-0.005536</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>-0.000495</v>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="K5" s="10" t="n">
         <v>0.000274</v>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="L5" s="10" t="n">
         <v>0.001657</v>
       </c>
-      <c r="L5" s="10" t="n">
+      <c r="M5" s="10" t="n">
         <v>0.001172</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="N5" s="10" t="n">
         <v>0.000102</v>
       </c>
-      <c r="N5" s="10" t="n">
+      <c r="O5" s="10" t="n">
         <v>0.000285</v>
-      </c>
-      <c r="O5" s="10" t="n">
-        <v>0.000374</v>
       </c>
     </row>
     <row r="6">
@@ -1233,44 +1233,44 @@
       <c r="B6" s="6" t="n">
         <v>-0.002505</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="10" t="n">
+        <v>0.000215</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>-0.000992</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="E6" s="10" t="n">
         <v>0.001854</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="F6" s="10" t="n">
         <v>0.001388</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>-0.001102</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="H6" s="10" t="n">
         <v>0.002665</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="I6" s="10" t="n">
         <v>0.005058</v>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="J6" s="10" t="n">
         <v>0.001982</v>
       </c>
-      <c r="J6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6" t="n">
+      <c r="K6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="6" t="n">
         <v>-0.001991</v>
       </c>
-      <c r="L6" s="10" t="n">
+      <c r="M6" s="10" t="n">
         <v>0.000369</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="N6" s="6" t="n">
         <v>-0.000499</v>
       </c>
-      <c r="N6" s="10" t="n">
+      <c r="O6" s="10" t="n">
         <v>0.0009779999999999999</v>
-      </c>
-      <c r="O6" s="10" t="n">
-        <v>0.000215</v>
       </c>
     </row>
     <row r="7">
@@ -1282,44 +1282,44 @@
       <c r="B7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C7" s="6" t="n">
+        <v>-0.001165</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>-0.002773</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="6" t="n">
         <v>-0.003548</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="6" t="n">
         <v>-0.003356</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="6" t="n">
         <v>-0.001785</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="6" t="n">
         <v>-0.004030000000000001</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="J7" s="6" t="n">
         <v>-0.003457</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="6" t="n">
         <v>-0.003274</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="L7" s="6" t="n">
         <v>-0.003561</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="6" t="n">
         <v>-0.002123</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="N7" s="6" t="n">
         <v>-0.001462</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="6" t="n">
         <v>-0.002977</v>
-      </c>
-      <c r="O7" s="6" t="n">
-        <v>-0.001165</v>
       </c>
     </row>
     <row r="8">
@@ -1331,44 +1331,44 @@
       <c r="B8" s="10" t="n">
         <v>0.000501</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="C8" s="6" t="n">
+        <v>-0.001051</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
         <v>-0.003683</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="6" t="n">
         <v>-0.003648</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="6" t="n">
         <v>-0.002056</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="6" t="n">
         <v>-0.005763000000000001</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="6" t="n">
         <v>-0.003514</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="J8" s="6" t="n">
         <v>-0.004425</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="6" t="n">
         <v>-0.000273</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="L8" s="6" t="n">
         <v>-0.002536</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="6" t="n">
         <v>-0.003766</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="N8" s="6" t="n">
         <v>-0.00172</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="6" t="n">
         <v>-0.002675</v>
-      </c>
-      <c r="O8" s="6" t="n">
-        <v>-0.001051</v>
       </c>
     </row>
     <row r="9">
@@ -1381,43 +1381,43 @@
         <v>-0.0025</v>
       </c>
       <c r="C9" s="10" t="n">
+        <v>8.999999999999999e-05</v>
+      </c>
+      <c r="D9" s="10" t="n">
         <v>0.000993</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="E9" s="10" t="n">
         <v>0.0009220000000000001</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="6" t="n">
         <v>-0.000169</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="G9" s="10" t="n">
         <v>0.001065</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="H9" s="10" t="n">
         <v>0.002827</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="I9" s="10" t="n">
         <v>0.001005</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="J9" s="10" t="n">
         <v>0.0009840000000000001</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>-0.002177</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="L9" s="10" t="n">
         <v>0.001008</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="M9" s="10" t="n">
         <v>0.000443</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="N9" s="10" t="n">
         <v>6.8e-05</v>
       </c>
-      <c r="N9" s="10" t="n">
+      <c r="O9" s="10" t="n">
         <v>0.0005369999999999999</v>
-      </c>
-      <c r="O9" s="10" t="n">
-        <v>8.999999999999999e-05</v>
       </c>
     </row>
     <row r="10">
@@ -1430,43 +1430,43 @@
         <v>-0.001498</v>
       </c>
       <c r="C10" s="6" t="n">
+        <v>-0.001354</v>
+      </c>
+      <c r="D10" s="6" t="n">
         <v>-0.002476</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="E10" s="6" t="n">
         <v>-0.001381</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="6" t="n">
         <v>-0.001943</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="6" t="n">
         <v>-0.005051</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="6" t="n">
         <v>-0.009876000000000001</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="6" t="n">
         <v>-0.0005020000000000001</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="J10" s="6" t="n">
         <v>-0.001474</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="6" t="n">
         <v>-0.003256</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="L10" s="6" t="n">
         <v>-0.004026</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="6" t="n">
         <v>-0.003679</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="N10" s="6" t="n">
         <v>-0.002089</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="6" t="n">
         <v>-0.002377</v>
-      </c>
-      <c r="O10" s="6" t="n">
-        <v>-0.001354</v>
       </c>
     </row>
     <row r="11">
@@ -1479,43 +1479,43 @@
         <v>-0.000499</v>
       </c>
       <c r="C11" s="6" t="n">
+        <v>-0.002049</v>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>-0.003455</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="E11" s="6" t="n">
         <v>-0.003668</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="6" t="n">
         <v>-0.00362</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="G11" s="10" t="n">
         <v>0.002396</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="6" t="n">
         <v>-0.001608</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="6" t="n">
         <v>-0.004002</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>-0.00489</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>-0.002166</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="L11" s="6" t="n">
         <v>-0.002881</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="6" t="n">
         <v>-0.003655</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="N11" s="6" t="n">
         <v>-0.002646</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="6" t="n">
         <v>-0.003236</v>
-      </c>
-      <c r="O11" s="6" t="n">
-        <v>-0.002049</v>
       </c>
     </row>
     <row r="12">
@@ -1527,44 +1527,44 @@
       <c r="B12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="10" t="n">
+        <v>0.0008899999999999999</v>
+      </c>
+      <c r="D12" s="6" t="n">
         <v>-0.00197</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="E12" s="10" t="n">
         <v>0.000459</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="F12" s="10" t="n">
         <v>0.000958</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="G12" s="10" t="n">
         <v>0.001012</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="H12" s="10" t="n">
         <v>0.001306</v>
       </c>
-      <c r="H12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="10" t="n">
+      <c r="I12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="10" t="n">
         <v>0.0009790000000000001</v>
       </c>
-      <c r="J12" s="10" t="n">
+      <c r="K12" s="10" t="n">
         <v>0.00217</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="L12" s="6" t="n">
         <v>-0.000413</v>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="M12" s="10" t="n">
         <v>0.000418</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="N12" s="10" t="n">
         <v>0.000225</v>
       </c>
-      <c r="N12" s="10" t="n">
+      <c r="O12" s="10" t="n">
         <v>5e-05</v>
-      </c>
-      <c r="O12" s="10" t="n">
-        <v>0.0008899999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1577,43 +1577,43 @@
         <v>0.000749</v>
       </c>
       <c r="C13" s="10" t="n">
+        <v>0.00062</v>
+      </c>
+      <c r="D13" s="10" t="n">
         <v>0.0009859999999999999</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="E13" s="10" t="n">
         <v>0.0009180000000000001</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="6" t="n">
         <v>-0.000357</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="6" t="n">
         <v>-0.00099</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="H13" s="10" t="n">
         <v>0.001883</v>
       </c>
-      <c r="H13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="10" t="n">
+      <c r="I13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="10" t="n">
         <v>0.00049</v>
       </c>
-      <c r="J13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="10" t="n">
+      <c r="K13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>0.000483</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="M13" s="10" t="n">
         <v>0.002752</v>
       </c>
-      <c r="M13" s="10" t="n">
+      <c r="N13" s="10" t="n">
         <v>1.1e-05</v>
       </c>
-      <c r="N13" s="10" t="n">
+      <c r="O13" s="10" t="n">
         <v>0.0007570000000000001</v>
-      </c>
-      <c r="O13" s="10" t="n">
-        <v>0.00062</v>
       </c>
     </row>
     <row r="14">
@@ -1625,44 +1625,44 @@
       <c r="B14" s="6" t="n">
         <v>-0.00025</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="10" t="n">
+        <v>0.000214</v>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>-0.000985</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="E14" s="6" t="n">
         <v>-0.0009170000000000001</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="6" t="n">
         <v>-0.000803</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="G14" s="10" t="n">
         <v>0.000552</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="H14" s="10" t="n">
         <v>0.001324</v>
       </c>
-      <c r="H14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="6" t="n">
         <v>-0.000489</v>
       </c>
-      <c r="J14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="10" t="n">
+      <c r="K14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10" t="n">
         <v>0.000105</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="6" t="n">
         <v>-0.0009130000000000001</v>
       </c>
-      <c r="M14" s="10" t="n">
+      <c r="N14" s="10" t="n">
         <v>7.900000000000001e-05</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="6" t="n">
         <v>-0.000202</v>
-      </c>
-      <c r="O14" s="10" t="n">
-        <v>0.000214</v>
       </c>
     </row>
     <row r="15">
@@ -1674,44 +1674,44 @@
       <c r="B15" s="10" t="n">
         <v>0.00125</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="6" t="n">
+        <v>-0.000169</v>
+      </c>
+      <c r="D15" s="10" t="n">
         <v>0.000246</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="E15" s="6" t="n">
         <v>-0.000229</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="F15" s="10" t="n">
         <v>0.000308</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="6" t="n">
         <v>-5.2e-05</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="H15" s="10" t="n">
         <v>0.003345</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="6" t="n">
         <v>-0.0001</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="J15" s="6" t="n">
         <v>-0.0009779999999999999</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>-0.0008129999999999999</v>
       </c>
-      <c r="K15" s="10" t="n">
+      <c r="L15" s="10" t="n">
         <v>0.000299</v>
       </c>
-      <c r="L15" s="10" t="n">
+      <c r="M15" s="10" t="n">
         <v>0.000656</v>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="N15" s="6" t="n">
         <v>-0.000439</v>
       </c>
-      <c r="N15" s="10" t="n">
+      <c r="O15" s="10" t="n">
         <v>4e-05</v>
-      </c>
-      <c r="O15" s="6" t="n">
-        <v>-0.000169</v>
       </c>
     </row>
     <row r="16">
@@ -1723,44 +1723,44 @@
       <c r="B16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="10" t="n">
+        <v>0.0008010000000000001</v>
+      </c>
+      <c r="D16" s="6" t="n">
         <v>-0.000492</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="E16" s="10" t="n">
         <v>0.001373</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="6" t="n">
         <v>-0.0006980000000000001</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="6" t="n">
         <v>-0.0018</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="H16" s="10" t="n">
         <v>0.001232</v>
       </c>
-      <c r="H16" s="10" t="n">
+      <c r="I16" s="10" t="n">
         <v>0.0009959999999999999</v>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="J16" s="10" t="n">
         <v>0.000974</v>
       </c>
-      <c r="J16" s="10" t="n">
+      <c r="K16" s="10" t="n">
         <v>0.002991</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="L16" s="10" t="n">
         <v>0.001038</v>
       </c>
-      <c r="L16" s="10" t="n">
+      <c r="M16" s="10" t="n">
         <v>0.001442</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="N16" s="10" t="n">
         <v>0.001477</v>
       </c>
-      <c r="N16" s="10" t="n">
+      <c r="O16" s="10" t="n">
         <v>0.00098</v>
-      </c>
-      <c r="O16" s="10" t="n">
-        <v>0.0008010000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1772,44 +1772,44 @@
       <c r="B17" s="6" t="n">
         <v>-0.0005</v>
       </c>
-      <c r="C17" s="7" t="n">
-        <v>0</v>
+      <c r="C17" s="6" t="n">
+        <v>-4.5e-05</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="10" t="n">
         <v>0.000196</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>-0.002574</v>
       </c>
-      <c r="G17" s="10" t="n">
+      <c r="H17" s="10" t="n">
         <v>0.002919</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="6" t="n">
         <v>-0.000495</v>
       </c>
-      <c r="I17" s="10" t="n">
+      <c r="J17" s="10" t="n">
         <v>0.00049</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="6" t="n">
         <v>-0.002062</v>
       </c>
-      <c r="K17" s="10" t="n">
+      <c r="L17" s="10" t="n">
         <v>0.0004660000000000001</v>
       </c>
-      <c r="L17" s="10" t="n">
+      <c r="M17" s="10" t="n">
         <v>0.000528</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="N17" s="6" t="n">
         <v>-4.5e-05</v>
       </c>
-      <c r="N17" s="10" t="n">
+      <c r="O17" s="10" t="n">
         <v>0.000445</v>
-      </c>
-      <c r="O17" s="6" t="n">
-        <v>-4.5e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1822,43 +1822,43 @@
         <v>0</v>
       </c>
       <c r="C18" s="10" t="n">
+        <v>0.000181</v>
+      </c>
+      <c r="D18" s="10" t="n">
         <v>0.0004929999999999999</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="E18" s="10" t="n">
         <v>0.000459</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="6" t="n">
         <v>-0.000935</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="G18" s="10" t="n">
         <v>0.000914</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="H18" s="10" t="n">
         <v>0.001812</v>
       </c>
-      <c r="H18" s="10" t="n">
+      <c r="I18" s="10" t="n">
         <v>0.0009970000000000001</v>
       </c>
-      <c r="I18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="6" t="n">
         <v>-0.000808</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="L18" s="6" t="n">
         <v>-0.000185</v>
       </c>
-      <c r="L18" s="10" t="n">
+      <c r="M18" s="10" t="n">
         <v>0.000399</v>
       </c>
-      <c r="M18" s="10" t="n">
+      <c r="N18" s="10" t="n">
         <v>0.0003500000000000001</v>
       </c>
-      <c r="N18" s="10" t="n">
+      <c r="O18" s="10" t="n">
         <v>1e-05</v>
-      </c>
-      <c r="O18" s="10" t="n">
-        <v>0.000181</v>
       </c>
     </row>
     <row r="19">
@@ -1871,43 +1871,43 @@
         <v>0.0005</v>
       </c>
       <c r="C19" s="6" t="n">
+        <v>-3.4e-05</v>
+      </c>
+      <c r="D19" s="6" t="n">
         <v>-0.000492</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="E19" s="10" t="n">
         <v>0.000225</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="F19" s="10" t="n">
         <v>0.000175</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="G19" s="10" t="n">
         <v>0.000915</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="H19" s="10" t="n">
         <v>0.001661</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="6" t="n">
         <v>-0.001496</v>
       </c>
-      <c r="I19" s="10" t="n">
+      <c r="J19" s="10" t="n">
         <v>0.0009750000000000001</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="6" t="n">
         <v>-0.0005419999999999999</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="L19" s="6" t="n">
         <v>-0.000273</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="6" t="n">
         <v>-0.000409</v>
       </c>
-      <c r="M19" s="10" t="n">
+      <c r="N19" s="10" t="n">
         <v>0.000914</v>
       </c>
-      <c r="N19" s="10" t="n">
+      <c r="O19" s="10" t="n">
         <v>0.000283</v>
-      </c>
-      <c r="O19" s="6" t="n">
-        <v>-3.4e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1919,44 +1919,44 @@
       <c r="B20" s="6" t="n">
         <v>-0.0005</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="10" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="D20" s="6" t="n">
         <v>-0.000487</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="E20" s="10" t="n">
         <v>0.0006900000000000001</v>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="F20" s="10" t="n">
         <v>0.0009220000000000001</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="6" t="n">
         <v>-3.1e-05</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="6" t="n">
         <v>-0.001427</v>
       </c>
-      <c r="H20" s="10" t="n">
+      <c r="I20" s="10" t="n">
         <v>0.001498</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="J20" s="6" t="n">
         <v>-0.0009750000000000001</v>
       </c>
-      <c r="J20" s="10" t="n">
+      <c r="K20" s="10" t="n">
         <v>0.001351</v>
       </c>
-      <c r="K20" s="10" t="n">
+      <c r="L20" s="10" t="n">
         <v>0.001083</v>
       </c>
-      <c r="L20" s="10" t="n">
+      <c r="M20" s="10" t="n">
         <v>0.0011</v>
       </c>
-      <c r="M20" s="10" t="n">
+      <c r="N20" s="10" t="n">
         <v>0.000339</v>
       </c>
-      <c r="N20" s="10" t="n">
+      <c r="O20" s="10" t="n">
         <v>0.000779</v>
-      </c>
-      <c r="O20" s="10" t="n">
-        <v>0.00044</v>
       </c>
     </row>
     <row r="21">
@@ -1969,43 +1969,43 @@
         <v>0.0005</v>
       </c>
       <c r="C21" s="10" t="n">
+        <v>0.000384</v>
+      </c>
+      <c r="D21" s="10" t="n">
         <v>0.001474</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="E21" s="10" t="n">
         <v>0.000916</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="F21" s="10" t="n">
         <v>0.001245</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="6" t="n">
         <v>-0.000114</v>
       </c>
-      <c r="G21" s="10" t="n">
+      <c r="H21" s="10" t="n">
         <v>0.004117</v>
       </c>
-      <c r="H21" s="10" t="n">
+      <c r="I21" s="10" t="n">
         <v>0.002501</v>
       </c>
-      <c r="I21" s="10" t="n">
+      <c r="J21" s="10" t="n">
         <v>0.001958</v>
       </c>
-      <c r="J21" s="10" t="n">
+      <c r="K21" s="10" t="n">
         <v>0.00217</v>
       </c>
-      <c r="K21" s="10" t="n">
+      <c r="L21" s="10" t="n">
         <v>0.001579</v>
       </c>
-      <c r="L21" s="10" t="n">
+      <c r="M21" s="10" t="n">
         <v>0.001566</v>
       </c>
-      <c r="M21" s="10" t="n">
+      <c r="N21" s="10" t="n">
         <v>0.001051</v>
       </c>
-      <c r="N21" s="10" t="n">
+      <c r="O21" s="10" t="n">
         <v>0.001012</v>
-      </c>
-      <c r="O21" s="10" t="n">
-        <v>0.000384</v>
       </c>
     </row>
     <row r="22">
@@ -2017,44 +2017,44 @@
       <c r="B22" s="10" t="n">
         <v>0.0009959999999999999</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="10" t="n">
+        <v>0.000723</v>
+      </c>
+      <c r="D22" s="6" t="n">
         <v>-0.001472</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="E22" s="10" t="n">
         <v>0.001609</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="F22" s="10" t="n">
         <v>0.001499</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="6" t="n">
         <v>-0.000644</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="6" t="n">
         <v>-0.003159</v>
       </c>
-      <c r="H22" s="10" t="n">
+      <c r="I22" s="10" t="n">
         <v>0.005032</v>
       </c>
-      <c r="I22" s="10" t="n">
+      <c r="J22" s="10" t="n">
         <v>0.00245</v>
       </c>
-      <c r="J22" s="10" t="n">
+      <c r="K22" s="10" t="n">
         <v>0.001896</v>
       </c>
-      <c r="K22" s="10" t="n">
+      <c r="L22" s="10" t="n">
         <v>0.002042</v>
       </c>
-      <c r="L22" s="10" t="n">
+      <c r="M22" s="10" t="n">
         <v>0.002729</v>
       </c>
-      <c r="M22" s="10" t="n">
+      <c r="N22" s="10" t="n">
         <v>0.002834</v>
       </c>
-      <c r="N22" s="10" t="n">
+      <c r="O22" s="10" t="n">
         <v>0.002059</v>
-      </c>
-      <c r="O22" s="10" t="n">
-        <v>0.000723</v>
       </c>
     </row>
     <row r="23">
@@ -2066,44 +2066,44 @@
       <c r="B23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C23" s="6" t="n">
+        <v>-0.000825</v>
+      </c>
+      <c r="D23" s="10" t="n">
         <v>0.001227</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="E23" s="10" t="n">
         <v>0.000692</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="F23" s="10" t="n">
         <v>0.000575</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="G23" s="10" t="n">
         <v>0.0008630000000000001</v>
       </c>
-      <c r="G23" s="10" t="n">
+      <c r="H23" s="10" t="n">
         <v>0.003183</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="6" t="n">
         <v>-0.001507</v>
       </c>
-      <c r="I23" s="10" t="n">
+      <c r="J23" s="10" t="n">
         <v>0.000492</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="6" t="n">
         <v>-0.000267</v>
       </c>
-      <c r="K23" s="10" t="n">
+      <c r="L23" s="10" t="n">
         <v>0.001026</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="6" t="n">
         <v>-0.00013</v>
       </c>
-      <c r="M23" s="6" t="n">
+      <c r="N23" s="6" t="n">
         <v>-0.000578</v>
       </c>
-      <c r="N23" s="10" t="n">
+      <c r="O23" s="10" t="n">
         <v>0.000365</v>
-      </c>
-      <c r="O23" s="6" t="n">
-        <v>-0.000825</v>
       </c>
     </row>
     <row r="24">
@@ -2116,43 +2116,43 @@
         <v>0.001002</v>
       </c>
       <c r="C24" s="10" t="n">
+        <v>0.000746</v>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>0.000246</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="E24" s="10" t="n">
         <v>0.000919</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="F24" s="10" t="n">
         <v>0.001327</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="G24" s="10" t="n">
         <v>0.001353</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="H24" s="10" t="n">
         <v>0.002007</v>
       </c>
-      <c r="H24" s="10" t="n">
+      <c r="I24" s="10" t="n">
         <v>0.003023</v>
       </c>
-      <c r="I24" s="10" t="n">
+      <c r="J24" s="10" t="n">
         <v>0.000487</v>
       </c>
-      <c r="J24" s="10" t="n">
+      <c r="K24" s="10" t="n">
         <v>0.00054</v>
       </c>
-      <c r="K24" s="10" t="n">
+      <c r="L24" s="10" t="n">
         <v>0.001347</v>
       </c>
-      <c r="L24" s="10" t="n">
+      <c r="M24" s="10" t="n">
         <v>0.002638</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="N24" s="10" t="n">
         <v>0.001055</v>
       </c>
-      <c r="N24" s="10" t="n">
+      <c r="O24" s="10" t="n">
         <v>0.001219</v>
-      </c>
-      <c r="O24" s="10" t="n">
-        <v>0.000746</v>
       </c>
     </row>
     <row r="25">
@@ -2165,43 +2165,43 @@
         <v>0</v>
       </c>
       <c r="C25" s="10" t="n">
+        <v>0.000317</v>
+      </c>
+      <c r="D25" s="10" t="n">
         <v>0.001471</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="E25" s="10" t="n">
         <v>0.000462</v>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="F25" s="10" t="n">
         <v>0.000239</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="6" t="n">
         <v>-0.004282</v>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="H25" s="10" t="n">
         <v>0.001671</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="6" t="n">
         <v>-0.000505</v>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="J25" s="10" t="n">
         <v>0.0004929999999999999</v>
       </c>
-      <c r="J25" s="10" t="n">
+      <c r="K25" s="10" t="n">
         <v>0.001632</v>
       </c>
-      <c r="K25" s="10" t="n">
+      <c r="L25" s="10" t="n">
         <v>0.000683</v>
       </c>
-      <c r="L25" s="10" t="n">
+      <c r="M25" s="10" t="n">
         <v>0.000163</v>
       </c>
-      <c r="M25" s="10" t="n">
+      <c r="N25" s="10" t="n">
         <v>0.000113</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="6" t="n">
         <v>-0.000163</v>
-      </c>
-      <c r="O25" s="10" t="n">
-        <v>0.000317</v>
       </c>
     </row>
     <row r="26">
@@ -2213,44 +2213,44 @@
       <c r="B26" s="10" t="n">
         <v>0.000998</v>
       </c>
-      <c r="C26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="10" t="n">
+      <c r="C26" s="10" t="n">
+        <v>0.000396</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10" t="n">
         <v>0.000458</v>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="F26" s="10" t="n">
         <v>0.000513</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="6" t="n">
         <v>-0.002038</v>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="H26" s="10" t="n">
         <v>0.005980999999999999</v>
       </c>
-      <c r="H26" s="10" t="n">
+      <c r="I26" s="10" t="n">
         <v>0.000505</v>
       </c>
-      <c r="I26" s="10" t="n">
+      <c r="J26" s="10" t="n">
         <v>0.0009810000000000001</v>
       </c>
-      <c r="J26" s="10" t="n">
+      <c r="K26" s="10" t="n">
         <v>0.001635</v>
       </c>
-      <c r="K26" s="10" t="n">
+      <c r="L26" s="10" t="n">
         <v>0.000364</v>
       </c>
-      <c r="L26" s="10" t="n">
+      <c r="M26" s="10" t="n">
         <v>0.000511</v>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="N26" s="10" t="n">
         <v>0.000499</v>
       </c>
-      <c r="N26" s="10" t="n">
+      <c r="O26" s="10" t="n">
         <v>0.000163</v>
-      </c>
-      <c r="O26" s="10" t="n">
-        <v>0.000396</v>
       </c>
     </row>
     <row r="27">
@@ -2262,44 +2262,44 @@
       <c r="B27" s="6" t="n">
         <v>-0.001497</v>
       </c>
-      <c r="C27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="10" t="n">
+      <c r="C27" s="10" t="n">
+        <v>0.000339</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10" t="n">
         <v>0.002772</v>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="F27" s="10" t="n">
         <v>0.000316</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="6" t="n">
         <v>-0.000879</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="6" t="n">
         <v>-0.008935999999999999</v>
       </c>
-      <c r="H27" s="10" t="n">
+      <c r="I27" s="10" t="n">
         <v>0.004555</v>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="J27" s="10" t="n">
         <v>0.0004929999999999999</v>
       </c>
-      <c r="J27" s="10" t="n">
+      <c r="K27" s="10" t="n">
         <v>0.000273</v>
       </c>
-      <c r="K27" s="10" t="n">
+      <c r="L27" s="10" t="n">
         <v>0.0009229999999999999</v>
       </c>
-      <c r="L27" s="10" t="n">
+      <c r="M27" s="10" t="n">
         <v>0.00197</v>
       </c>
-      <c r="M27" s="10" t="n">
+      <c r="N27" s="10" t="n">
         <v>0.0006469999999999999</v>
       </c>
-      <c r="N27" s="10" t="n">
+      <c r="O27" s="10" t="n">
         <v>0.001058</v>
-      </c>
-      <c r="O27" s="10" t="n">
-        <v>0.000339</v>
       </c>
     </row>
     <row r="28">
@@ -2312,43 +2312,43 @@
         <v>0.001002</v>
       </c>
       <c r="C28" s="10" t="n">
+        <v>0.000623</v>
+      </c>
+      <c r="D28" s="10" t="n">
         <v>0.000494</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="E28" s="6" t="n">
         <v>-0.001384</v>
       </c>
-      <c r="E28" s="10" t="n">
+      <c r="F28" s="10" t="n">
         <v>0.000183</v>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="G28" s="10" t="n">
         <v>0.0006619999999999999</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="6" t="n">
         <v>-0.001124</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="6" t="n">
         <v>-0.001009</v>
       </c>
-      <c r="I28" s="10" t="n">
+      <c r="J28" s="10" t="n">
         <v>0.000494</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="6" t="n">
         <v>-0.000273</v>
       </c>
-      <c r="K28" s="6" t="n">
+      <c r="L28" s="6" t="n">
         <v>-0.00047</v>
       </c>
-      <c r="L28" s="10" t="n">
+      <c r="M28" s="10" t="n">
         <v>4.400000000000001e-05</v>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="N28" s="10" t="n">
         <v>0.000432</v>
       </c>
-      <c r="N28" s="10" t="n">
+      <c r="O28" s="10" t="n">
         <v>0.000122</v>
-      </c>
-      <c r="O28" s="10" t="n">
-        <v>0.000623</v>
       </c>
     </row>
     <row r="29">
@@ -2360,44 +2360,44 @@
       <c r="B29" s="6" t="n">
         <v>-0.000501</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C29" s="10" t="n">
+        <v>0.00026</v>
+      </c>
+      <c r="D29" s="6" t="n">
         <v>-0.000494</v>
       </c>
-      <c r="D29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6" t="n">
         <v>-9.1e-05</v>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="G29" s="10" t="n">
         <v>0.0005899999999999999</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="H29" s="10" t="n">
         <v>0.00392</v>
       </c>
-      <c r="H29" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="I29" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="10" t="n">
+      <c r="J29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="10" t="n">
         <v>0.0008210000000000001</v>
       </c>
-      <c r="K29" s="10" t="n">
+      <c r="L29" s="10" t="n">
         <v>0.000257</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="6" t="n">
         <v>-1.1e-05</v>
       </c>
-      <c r="M29" s="6" t="n">
+      <c r="N29" s="6" t="n">
         <v>-0.000204</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="6" t="n">
         <v>-0.000122</v>
-      </c>
-      <c r="O29" s="10" t="n">
-        <v>0.00026</v>
       </c>
     </row>
     <row r="30">
@@ -2409,44 +2409,44 @@
       <c r="B30" s="10" t="n">
         <v>0.000501</v>
       </c>
-      <c r="C30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="6" t="n">
+      <c r="C30" s="10" t="n">
+        <v>0.000193</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="6" t="n">
         <v>-0.000463</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="6" t="n">
         <v>-6.3e-05</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="G30" s="10" t="n">
         <v>8.3e-05</v>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="H30" s="10" t="n">
         <v>7e-06</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="6" t="n">
         <v>-0.001014</v>
       </c>
-      <c r="I30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="6" t="n">
+      <c r="J30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="6" t="n">
         <v>-0.001361</v>
       </c>
-      <c r="K30" s="10" t="n">
+      <c r="L30" s="10" t="n">
         <v>0.001244</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="6" t="n">
         <v>-0.0009239999999999999</v>
       </c>
-      <c r="M30" s="10" t="n">
+      <c r="N30" s="10" t="n">
         <v>0.0005909999999999999</v>
       </c>
-      <c r="N30" s="10" t="n">
+      <c r="O30" s="10" t="n">
         <v>0.000376</v>
-      </c>
-      <c r="O30" s="10" t="n">
-        <v>0.000193</v>
       </c>
     </row>
     <row r="31">
@@ -2458,44 +2458,44 @@
       <c r="B31" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="10" t="n">
+      <c r="C31" s="10" t="n">
+        <v>0.000136</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="10" t="n">
         <v>0.0009260000000000001</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="6" t="n">
         <v>-0.000239</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="6" t="n">
         <v>-0.001354</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="6" t="n">
         <v>-0.011534</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="6" t="n">
         <v>-0.000501</v>
       </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="6" t="n">
         <v>-0.002176</v>
       </c>
-      <c r="K31" s="6" t="n">
+      <c r="L31" s="6" t="n">
         <v>-0.00079</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="6" t="n">
         <v>-0.000619</v>
       </c>
-      <c r="M31" s="6" t="n">
+      <c r="N31" s="6" t="n">
         <v>-0.000398</v>
       </c>
-      <c r="N31" s="10" t="n">
+      <c r="O31" s="10" t="n">
         <v>0.000428</v>
-      </c>
-      <c r="O31" s="10" t="n">
-        <v>0.000136</v>
       </c>
     </row>
     <row r="32">
@@ -2508,43 +2508,43 @@
         <v>0.000998</v>
       </c>
       <c r="C32" s="10" t="n">
+        <v>6.8e-05</v>
+      </c>
+      <c r="D32" s="10" t="n">
         <v>0.0009829999999999999</v>
       </c>
-      <c r="D32" s="10" t="n">
+      <c r="E32" s="10" t="n">
         <v>0.0009220000000000001</v>
       </c>
-      <c r="E32" s="10" t="n">
+      <c r="F32" s="10" t="n">
         <v>0.000309</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="6" t="n">
         <v>-0.000548</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="6" t="n">
         <v>-0.002343</v>
       </c>
-      <c r="H32" s="10" t="n">
+      <c r="I32" s="10" t="n">
         <v>0.0005020000000000001</v>
       </c>
-      <c r="I32" s="10" t="n">
+      <c r="J32" s="10" t="n">
         <v>0.0009829999999999999</v>
       </c>
-      <c r="J32" s="10" t="n">
+      <c r="K32" s="10" t="n">
         <v>0.001633</v>
       </c>
-      <c r="K32" s="6" t="n">
+      <c r="L32" s="6" t="n">
         <v>-0.000337</v>
       </c>
-      <c r="L32" s="10" t="n">
+      <c r="M32" s="10" t="n">
         <v>0.000555</v>
       </c>
-      <c r="M32" s="6" t="n">
+      <c r="N32" s="6" t="n">
         <v>-0.000136</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="6" t="n">
         <v>-0.000204</v>
-      </c>
-      <c r="O32" s="10" t="n">
-        <v>6.8e-05</v>
       </c>
     </row>
     <row r="33">
@@ -2557,43 +2557,43 @@
         <v>0</v>
       </c>
       <c r="C33" s="10" t="n">
+        <v>0.000159</v>
+      </c>
+      <c r="D33" s="10" t="n">
         <v>0.000494</v>
       </c>
-      <c r="D33" s="10" t="n">
+      <c r="E33" s="10" t="n">
         <v>0.0004639999999999999</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="6" t="n">
         <v>-4.9e-05</v>
       </c>
-      <c r="F33" s="10" t="n">
+      <c r="G33" s="10" t="n">
         <v>0.000837</v>
       </c>
-      <c r="G33" s="10" t="n">
+      <c r="H33" s="10" t="n">
         <v>0.002943</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="6" t="n">
         <v>-0.001513</v>
       </c>
-      <c r="I33" s="10" t="n">
+      <c r="J33" s="10" t="n">
         <v>0.000494</v>
       </c>
-      <c r="J33" s="10" t="n">
+      <c r="K33" s="10" t="n">
         <v>0.002184</v>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="L33" s="6" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="6" t="n">
         <v>-2.2e-05</v>
       </c>
-      <c r="M33" s="6" t="n">
+      <c r="N33" s="6" t="n">
         <v>-0.00101</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="6" t="n">
         <v>-0.000285</v>
-      </c>
-      <c r="O33" s="10" t="n">
-        <v>0.000159</v>
       </c>
     </row>
     <row r="34">
@@ -2605,44 +2605,44 @@
       <c r="B34" s="10" t="n">
         <v>0.000452</v>
       </c>
-      <c r="C34" s="6" t="n">
+      <c r="C34" s="10" t="n">
+        <v>0.000317</v>
+      </c>
+      <c r="D34" s="6" t="n">
         <v>-0.00123</v>
       </c>
-      <c r="D34" s="10" t="n">
+      <c r="E34" s="10" t="n">
         <v>0.000232</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="6" t="n">
         <v>-0.00073</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="6" t="n">
         <v>-0.000992</v>
       </c>
-      <c r="G34" s="10" t="n">
+      <c r="H34" s="10" t="n">
         <v>0.000153</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="6" t="n">
         <v>-0.002111</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="J34" s="6" t="n">
         <v>-0.001968</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="6" t="n">
         <v>-0.002179</v>
       </c>
-      <c r="K34" s="6" t="n">
+      <c r="L34" s="6" t="n">
         <v>-0.001072</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="6" t="n">
         <v>-0.000739</v>
       </c>
-      <c r="M34" s="6" t="n">
+      <c r="N34" s="6" t="n">
         <v>-0.0009180000000000001</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="6" t="n">
         <v>-0.00126</v>
-      </c>
-      <c r="O34" s="10" t="n">
-        <v>0.000317</v>
       </c>
     </row>
     <row r="35">
@@ -2655,43 +2655,43 @@
         <v>0.000497</v>
       </c>
       <c r="C35" s="10" t="n">
+        <v>0.001158</v>
+      </c>
+      <c r="D35" s="10" t="n">
         <v>0.0009790000000000001</v>
       </c>
-      <c r="D35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="10" t="n">
+      <c r="E35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="10" t="n">
         <v>0.00197</v>
       </c>
-      <c r="F35" s="10" t="n">
+      <c r="G35" s="10" t="n">
         <v>0.000207</v>
       </c>
-      <c r="G35" s="10" t="n">
+      <c r="H35" s="10" t="n">
         <v>0.004125</v>
       </c>
-      <c r="H35" s="10" t="n">
+      <c r="I35" s="10" t="n">
         <v>0.001001</v>
       </c>
-      <c r="I35" s="10" t="n">
+      <c r="J35" s="10" t="n">
         <v>0.002949</v>
       </c>
-      <c r="J35" s="10" t="n">
+      <c r="K35" s="10" t="n">
         <v>0.001088</v>
       </c>
-      <c r="K35" s="10" t="n">
+      <c r="L35" s="10" t="n">
         <v>0.001696</v>
       </c>
-      <c r="L35" s="10" t="n">
+      <c r="M35" s="10" t="n">
         <v>0.001949</v>
       </c>
-      <c r="M35" s="10" t="n">
+      <c r="N35" s="10" t="n">
         <v>0.001067</v>
       </c>
-      <c r="N35" s="10" t="n">
+      <c r="O35" s="10" t="n">
         <v>0.001822</v>
-      </c>
-      <c r="O35" s="10" t="n">
-        <v>0.001158</v>
       </c>
     </row>
     <row r="36">
@@ -2703,44 +2703,44 @@
       <c r="B36" s="10" t="n">
         <v>0.0005020000000000001</v>
       </c>
-      <c r="C36" s="10" t="n">
+      <c r="C36" s="6" t="n">
+        <v>-0.000272</v>
+      </c>
+      <c r="D36" s="10" t="n">
         <v>0.001961</v>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="E36" s="10" t="n">
         <v>0.000459</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="6" t="n">
         <v>-0.00038</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="6" t="n">
         <v>-0.000341</v>
       </c>
-      <c r="G36" s="10" t="n">
+      <c r="H36" s="10" t="n">
         <v>0.0007149999999999999</v>
       </c>
-      <c r="H36" s="10" t="n">
+      <c r="I36" s="10" t="n">
         <v>0.0005059999999999999</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="J36" s="6" t="n">
         <v>-0.000495</v>
       </c>
-      <c r="J36" s="10" t="n">
+      <c r="K36" s="10" t="n">
         <v>0.001912</v>
       </c>
-      <c r="K36" s="6" t="n">
+      <c r="L36" s="6" t="n">
         <v>-0.000719</v>
       </c>
-      <c r="L36" s="10" t="n">
+      <c r="M36" s="10" t="n">
         <v>0.000414</v>
       </c>
-      <c r="M36" s="6" t="n">
+      <c r="N36" s="6" t="n">
         <v>-0.000556</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="6" t="n">
         <v>-0.000326</v>
-      </c>
-      <c r="O36" s="6" t="n">
-        <v>-0.000272</v>
       </c>
     </row>
     <row r="37">
@@ -2753,43 +2753,43 @@
         <v>0</v>
       </c>
       <c r="C37" s="10" t="n">
+        <v>0.000931</v>
+      </c>
+      <c r="D37" s="10" t="n">
         <v>0.000982</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="E37" s="10" t="n">
         <v>0.002307</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="F37" s="10" t="n">
         <v>0.001437</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="G37" s="10" t="n">
         <v>0.001137</v>
       </c>
-      <c r="G37" s="10" t="n">
+      <c r="H37" s="10" t="n">
         <v>0.005277</v>
       </c>
-      <c r="H37" s="10" t="n">
+      <c r="I37" s="10" t="n">
         <v>0.002012</v>
       </c>
-      <c r="I37" s="10" t="n">
+      <c r="J37" s="10" t="n">
         <v>0.001476</v>
       </c>
-      <c r="J37" s="10" t="n">
+      <c r="K37" s="10" t="n">
         <v>0.002521</v>
       </c>
-      <c r="K37" s="10" t="n">
+      <c r="L37" s="10" t="n">
         <v>0.001493</v>
       </c>
-      <c r="L37" s="10" t="n">
+      <c r="M37" s="10" t="n">
         <v>0.001167</v>
       </c>
-      <c r="M37" s="10" t="n">
+      <c r="N37" s="10" t="n">
         <v>0.00067</v>
       </c>
-      <c r="N37" s="10" t="n">
+      <c r="O37" s="10" t="n">
         <v>0.000896</v>
-      </c>
-      <c r="O37" s="10" t="n">
-        <v>0.000931</v>
       </c>
     </row>
     <row r="38">
@@ -2801,44 +2801,44 @@
       <c r="B38" s="10" t="n">
         <v>0.000498</v>
       </c>
-      <c r="C38" s="6" t="n">
+      <c r="C38" s="10" t="n">
+        <v>0.0007729999999999999</v>
+      </c>
+      <c r="D38" s="6" t="n">
         <v>-0.000491</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="E38" s="6" t="n">
         <v>-0.00046</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="F38" s="10" t="n">
         <v>0.00067</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="G38" s="10" t="n">
         <v>0.000569</v>
       </c>
-      <c r="G38" s="10" t="n">
+      <c r="H38" s="10" t="n">
         <v>0.003095</v>
       </c>
-      <c r="H38" s="10" t="n">
+      <c r="I38" s="10" t="n">
         <v>0.006077</v>
       </c>
-      <c r="I38" s="10" t="n">
+      <c r="J38" s="10" t="n">
         <v>0.001478</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="6" t="n">
         <v>-0.003813</v>
       </c>
-      <c r="K38" s="10" t="n">
+      <c r="L38" s="10" t="n">
         <v>0.001067</v>
       </c>
-      <c r="L38" s="10" t="n">
+      <c r="M38" s="10" t="n">
         <v>0.002229</v>
       </c>
-      <c r="M38" s="10" t="n">
+      <c r="N38" s="10" t="n">
         <v>0.00166</v>
       </c>
-      <c r="N38" s="10" t="n">
+      <c r="O38" s="10" t="n">
         <v>0.001336</v>
-      </c>
-      <c r="O38" s="10" t="n">
-        <v>0.0007729999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -2850,42 +2850,42 @@
       <c r="B39" s="6" t="n">
         <v>-0.001496</v>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" s="10" t="n">
+      <c r="C39" s="6" t="n">
+        <v>-0.0007040000000000001</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" s="10" t="n">
         <v>0.00046</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="6" t="n">
         <v>-0.001632</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="6" t="n">
         <v>-0.001745</v>
       </c>
-      <c r="G39" s="10" t="n">
+      <c r="H39" s="10" t="n">
         <v>0.000438</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="6" t="n">
         <v>-0.012007</v>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="J39" s="6" t="n">
         <v>-0.001965</v>
       </c>
-      <c r="J39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="6" t="n">
+      <c r="K39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="6" t="n">
         <v>-0.002555</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="6" t="n">
         <v>-0.003853</v>
       </c>
-      <c r="M39" s="6" t="n">
+      <c r="N39" s="6" t="n">
         <v>-0.002642</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="6" t="n">
         <v>-0.002249</v>
-      </c>
-      <c r="O39" s="6" t="n">
-        <v>-0.0007040000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -2897,42 +2897,42 @@
       <c r="B40" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" s="6" t="n">
+      <c r="C40" s="10" t="n">
+        <v>0.000329</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" s="6" t="n">
         <v>-0.001379</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="6" t="n">
         <v>-0.000295</v>
       </c>
-      <c r="F40" s="10" t="n">
+      <c r="G40" s="10" t="n">
         <v>0.000527</v>
       </c>
-      <c r="G40" s="10" t="n">
+      <c r="H40" s="10" t="n">
         <v>0.000906</v>
       </c>
-      <c r="H40" s="10" t="n">
+      <c r="I40" s="10" t="n">
         <v>0.005536</v>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="J40" s="6" t="n">
         <v>-0.0009840000000000001</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="6" t="n">
         <v>-0.002712</v>
       </c>
-      <c r="K40" s="6" t="n">
+      <c r="L40" s="6" t="n">
         <v>-0.000355</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="6" t="n">
         <v>-0.001066</v>
       </c>
-      <c r="M40" s="6" t="n">
+      <c r="N40" s="6" t="n">
         <v>-0.000215</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="6" t="n">
         <v>-0.000478</v>
-      </c>
-      <c r="O40" s="10" t="n">
-        <v>0.000329</v>
       </c>
     </row>
     <row r="41">
@@ -2945,40 +2945,40 @@
         <v>0</v>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" s="6" t="n">
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" s="6" t="n">
         <v>-0.0004639999999999999</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="6" t="n">
         <v>-0.000787</v>
       </c>
-      <c r="F41" s="10" t="n">
+      <c r="G41" s="10" t="n">
         <v>0.000724</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="6" t="n">
         <v>-0.001343</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="6" t="n">
         <v>-0.002511</v>
       </c>
-      <c r="I41" s="6" t="n">
+      <c r="J41" s="6" t="n">
         <v>-0.0009779999999999999</v>
       </c>
-      <c r="J41" s="10" t="n">
+      <c r="K41" s="10" t="n">
         <v>0.002176</v>
       </c>
-      <c r="K41" s="6" t="n">
+      <c r="L41" s="6" t="n">
         <v>-0.0006469999999999999</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="6" t="n">
         <v>-0.001542</v>
       </c>
-      <c r="M41" s="6" t="n">
+      <c r="N41" s="6" t="n">
         <v>-0.001268</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="6" t="n">
         <v>-0.000661</v>
       </c>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2990,40 +2990,40 @@
         <v>0.000497</v>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" s="10" t="n">
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" s="10" t="n">
         <v>0.000925</v>
       </c>
-      <c r="E42" s="10" t="n">
+      <c r="F42" s="10" t="n">
         <v>0.000746</v>
       </c>
-      <c r="F42" s="10" t="n">
+      <c r="G42" s="10" t="n">
         <v>0.000724</v>
       </c>
-      <c r="G42" s="10" t="n">
+      <c r="H42" s="10" t="n">
         <v>0.000467</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="6" t="n">
         <v>-0.001503</v>
       </c>
-      <c r="I42" s="10" t="n">
+      <c r="J42" s="10" t="n">
         <v>0.002457</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="6" t="n">
         <v>-0.001632</v>
       </c>
-      <c r="K42" s="10" t="n">
+      <c r="L42" s="10" t="n">
         <v>0.00023</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="6" t="n">
         <v>-0.000293</v>
       </c>
-      <c r="M42" s="10" t="n">
+      <c r="N42" s="10" t="n">
         <v>0.00026</v>
       </c>
-      <c r="N42" s="10" t="n">
+      <c r="O42" s="10" t="n">
         <v>0.00057</v>
       </c>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3035,40 +3035,40 @@
         <v>0.0005020000000000001</v>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" s="10" t="n">
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" s="10" t="n">
         <v>0.00231</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="F43" s="10" t="n">
         <v>0.001465</v>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="G43" s="10" t="n">
         <v>0.000311</v>
       </c>
-      <c r="G43" s="10" t="n">
+      <c r="H43" s="10" t="n">
         <v>0.001147</v>
       </c>
-      <c r="H43" s="10" t="n">
+      <c r="I43" s="10" t="n">
         <v>0.002513</v>
       </c>
-      <c r="I43" s="10" t="n">
+      <c r="J43" s="10" t="n">
         <v>0.001975</v>
       </c>
-      <c r="J43" s="10" t="n">
+      <c r="K43" s="10" t="n">
         <v>0.000546</v>
       </c>
-      <c r="K43" s="10" t="n">
+      <c r="L43" s="10" t="n">
         <v>0.0007630000000000001</v>
       </c>
-      <c r="L43" s="10" t="n">
+      <c r="M43" s="10" t="n">
         <v>0.001337</v>
       </c>
-      <c r="M43" s="10" t="n">
+      <c r="N43" s="10" t="n">
         <v>0.0016</v>
       </c>
-      <c r="N43" s="10" t="n">
+      <c r="O43" s="10" t="n">
         <v>0.001375</v>
       </c>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3080,40 +3080,40 @@
         <v>0</v>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" s="6" t="n">
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" s="6" t="n">
         <v>-0.000461</v>
       </c>
-      <c r="E44" s="10" t="n">
+      <c r="F44" s="10" t="n">
         <v>5.6e-05</v>
       </c>
-      <c r="F44" s="10" t="n">
+      <c r="G44" s="10" t="n">
         <v>0.000964</v>
       </c>
-      <c r="G44" s="10" t="n">
+      <c r="H44" s="10" t="n">
         <v>0.000552</v>
       </c>
-      <c r="H44" s="10" t="n">
+      <c r="I44" s="10" t="n">
         <v>0.002515</v>
       </c>
-      <c r="I44" s="6" t="n">
+      <c r="J44" s="6" t="n">
         <v>-0.000496</v>
       </c>
-      <c r="J44" s="10" t="n">
+      <c r="K44" s="10" t="n">
         <v>0.002997</v>
       </c>
-      <c r="K44" s="10" t="n">
+      <c r="L44" s="10" t="n">
         <v>0.000319</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="6" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="M44" s="10" t="n">
+      <c r="N44" s="10" t="n">
         <v>0.000942</v>
       </c>
-      <c r="N44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
